--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512474_ELIMINGRD14FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512474_ELIMINGRD14FINAL_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. VERKERK</t>
+          <t>C. COBOS ORTEGA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8289</v>
+        <v>6.1746</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4933</v>
+        <v>6.1658</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3356</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5462</v>
+        <v>6.4564</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9043</v>
+        <v>-0.5368000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.358</v>
+        <v>6.9932</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0269</v>
+        <v>6.8194</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5411</v>
+        <v>-0.2001</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5142</v>
+        <v>7.0194</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5194</v>
+        <v>-0.363</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3632</v>
+        <v>-0.3367</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1562</v>
+        <v>-0.0262</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.3895</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2006</v>
+        <v>2.5316</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3427</v>
+        <v>-0.3918</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2675</v>
+        <v>-0.012</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0752</v>
+        <v>-0.3798</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.2795</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3995</v>
+        <v>1.5005</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.4596</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. COBOS ORTEGA</t>
+          <t>J. VERKERK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.655</v>
+        <v>4.6337</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7456</v>
+        <v>3.6247</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0906</v>
+        <v>1.009</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4242</v>
+        <v>2.5908</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.486</v>
+        <v>2.9311</v>
       </c>
       <c r="I3" t="n">
-        <v>6.9103</v>
+        <v>-0.3403</v>
       </c>
       <c r="J3" t="n">
-        <v>6.6265</v>
+        <v>2.1867</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2563</v>
+        <v>2.6402</v>
       </c>
       <c r="L3" t="n">
-        <v>6.8828</v>
+        <v>-0.4535</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2023</v>
+        <v>0.4041</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2297</v>
+        <v>0.2909</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0274</v>
+        <v>0.1132</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4001</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R3" t="n">
-        <v>2.6007</v>
+        <v>2.1421</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9096</v>
+        <v>1.1013</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1399</v>
+        <v>1.138</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.0367</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2598</v>
+        <v>0.9416</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4596</v>
+        <v>2.4421</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7194</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4724</v>
+        <v>3.1697</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3808</v>
+        <v>1.2703</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0917</v>
+        <v>1.8993</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9379</v>
+        <v>0.9292</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1</v>
+        <v>0.1026</v>
       </c>
       <c r="I4" t="n">
-        <v>0.838</v>
+        <v>0.8266</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0256</v>
+        <v>0.1028</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6562</v>
+        <v>-0.6106</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6818</v>
+        <v>0.7134</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9123</v>
+        <v>0.8264</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7562</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1562</v>
+        <v>0.1132</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4655</v>
+        <v>0.2404</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6446</v>
+        <v>0.1412</v>
       </c>
       <c r="U4" t="n">
-        <v>0.179</v>
+        <v>0.0992</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. IBANEZ FIDALGO</t>
+          <t>P. IBÁÑEZ FIDALGO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7126</v>
+        <v>1.5237</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.4963</v>
+        <v>1.5237</v>
       </c>
       <c r="F5" t="n">
-        <v>4.2089</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8346</v>
+        <v>1.5237</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9576</v>
+        <v>0.3079</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.123</v>
+        <v>1.2158</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8163</v>
+        <v>1.5237</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8449</v>
+        <v>0.3079</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0286</v>
+        <v>1.2158</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0183</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1127</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0945</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.0009</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-6.0017</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0009</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0192</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8294</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1898</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8597</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8597</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. IBÁÑEZ FIDALGO</t>
+          <t>P. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4997</v>
+        <v>1.5005</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4997</v>
+        <v>-0.297</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.7975</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4997</v>
+        <v>1.7182</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2999</v>
+        <v>1.0483</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1998</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4997</v>
+        <v>1.1206</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2999</v>
+        <v>0.4311</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1998</v>
+        <v>0.6896</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.5975</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.6172</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.0197</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1684</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.1421</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.3013</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.2492</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.0522</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. CASTRO BRAVO</t>
+          <t>P. IBANEZ FIDALGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7705</v>
+        <v>1.1994</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0489</v>
+        <v>-2.1485</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8194</v>
+        <v>3.3479</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6936</v>
+        <v>1.9121</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2069</v>
+        <v>1.9782</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4868</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08</v>
+        <v>2.0947</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.9886</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08</v>
+        <v>0.1061</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6137</v>
+        <v>-0.1827</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2069</v>
+        <v>-0.0104</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4068</v>
+        <v>-0.1723</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4001</v>
+        <v>-2.921</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-5.8421</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4001</v>
+        <v>2.921</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3232</v>
+        <v>1.3184</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1289</v>
+        <v>0.7088</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1943</v>
+        <v>0.6096</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7298</v>
+        <v>0.9759</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5823</v>
+        <v>0.1197</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3122</v>
+        <v>0.8563</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0371</v>
+        <v>1.0905</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2127</v>
+        <v>1.2639</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1756</v>
+        <v>-0.1734</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6671</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2633</v>
+        <v>1.3599</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5961</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.37</v>
+        <v>0.2896</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0505</v>
+        <v>-0.096</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4205</v>
+        <v>0.3856</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0122</v>
+        <v>1.2496</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4913</v>
+        <v>0.9866</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5209</v>
+        <v>0.263</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1195</v>
+        <v>-1.1695</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3793</v>
+        <v>-1.449</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ SANCHEZ</t>
+          <t>S. CASTRO BRAVO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5847</v>
+        <v>0.7853</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1645</v>
+        <v>0.0571</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7492</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7155</v>
+        <v>0.6732</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1255</v>
+        <v>0.1934</v>
       </c>
       <c r="I9" t="n">
-        <v>0.59</v>
+        <v>0.4798</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9893</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4199</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5694</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7262</v>
+        <v>0.5921</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7057</v>
+        <v>0.1934</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0206</v>
+        <v>0.3987</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0003</v>
+        <v>0.3895</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2003</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2006</v>
+        <v>0.3895</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2715</v>
+        <v>-0.2773</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9535</v>
+        <v>-0.024</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.318</v>
+        <v>-0.2533</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8597</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. RAGA RODRIGUEZ</t>
+          <t>J. MUÑOZ LEIVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.579</v>
+        <v>0.3079</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4813</v>
+        <v>0.3079</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0603</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0999</v>
+        <v>0.3079</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0979</v>
+        <v>0.3079</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1978</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3342</v>
+        <v>0.3079</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0582</v>
+        <v>0.3079</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.276</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2343</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1561</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9218</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2006</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2003</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.059</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8537</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2053</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6202</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MUÑOZ LEIVA</t>
+          <t>R. RAGA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2999</v>
+        <v>0.1786</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2999</v>
+        <v>-1.7809</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1.9596</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2999</v>
+        <v>-1.1089</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2999</v>
+        <v>1.0956</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-2.2045</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2999</v>
+        <v>-1.2761</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2999</v>
+        <v>-0.0282</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-1.248</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.1672</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.1237</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.9565</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.1421</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.6576</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.4163</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.2413</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.6037</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0645</v>
+        <v>-0.0618</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1381,19 +1381,19 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0645</v>
+        <v>-0.0618</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0645</v>
+        <v>-0.0618</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2934</v>
+        <v>-1.4062</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.999</v>
+        <v>-2.042</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7056</v>
+        <v>0.6358</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7852</v>
+        <v>-0.7367</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.6902</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1436</v>
+        <v>-0.0465</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.7355</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.598</v>
+        <v>-0.5824</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3066</v>
+        <v>-0.1531</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1194</v>
+        <v>-0.0012</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0436</v>
+        <v>-0.1078</v>
       </c>
       <c r="O13" t="n">
-        <v>0.163</v>
+        <v>0.1067</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9681</v>
+        <v>-0.1437</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9535</v>
+        <v>-0.2492</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0146</v>
+        <v>0.1054</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.8459</v>
+        <v>-4.7596</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6873</v>
+        <v>-1.3997</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.1586</v>
+        <v>-3.3599</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1059</v>
+        <v>-1.1721</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.6531</v>
+        <v>-2.6858</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5472</v>
+        <v>1.5138</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9543</v>
+        <v>-0.8893</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.2742</v>
+        <v>-1.2135</v>
       </c>
       <c r="L14" t="n">
-        <v>0.32</v>
+        <v>0.3242</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1516</v>
+        <v>-0.2828</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3789</v>
+        <v>-1.4723</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2273</v>
+        <v>1.1896</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S14" t="n">
-        <v>0.859</v>
+        <v>0.102</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2672</v>
+        <v>0.4633</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4082</v>
+        <v>-0.3613</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.1992</v>
+        <v>-4.2737</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.1992</v>
+        <v>-4.2737</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>14.1288</v>
+        <v>14.4164</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8952</v>
+        <v>5.339300000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>11.2338</v>
+        <v>9.077299999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>13.9977</v>
+        <v>14.1843</v>
       </c>
       <c r="H15" t="n">
-        <v>5.423999999999999</v>
+        <v>5.316099999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>8.574100000000001</v>
+        <v>8.8683</v>
       </c>
       <c r="J15" t="n">
-        <v>10.8381</v>
+        <v>12.1369</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8261</v>
+        <v>4.4008</v>
       </c>
       <c r="L15" t="n">
-        <v>7.012300000000002</v>
+        <v>7.736000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1597</v>
+        <v>2.0472</v>
       </c>
       <c r="N15" t="n">
-        <v>1.5981</v>
+        <v>0.9151999999999998</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5617</v>
+        <v>1.1323</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.0004</v>
+        <v>-0.9735999999999996</v>
       </c>
       <c r="Q15" t="n">
-        <v>-19.0054</v>
+        <v>-18.5</v>
       </c>
       <c r="R15" t="n">
-        <v>18.0051</v>
+        <v>17.5262</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2897</v>
+        <v>3.4934</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8242</v>
+        <v>3.258</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4654000000000001</v>
+        <v>0.2351999999999998</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.1586</v>
+        <v>-2.2874</v>
       </c>
       <c r="W15" t="n">
-        <v>8.2379</v>
+        <v>8.4443</v>
       </c>
       <c r="X15" t="n">
-        <v>-10.3966</v>
+        <v>-10.7317</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>J. RICARDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3709</v>
+        <v>1.7614</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4682</v>
+        <v>2.6065</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8391</v>
+        <v>-0.8451</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.8299</v>
+        <v>-2.4683</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3844</v>
+        <v>-2.5672</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4455</v>
+        <v>0.0989</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.4851</v>
+        <v>0.1328</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.6051</v>
+        <v>-1.6265</v>
       </c>
       <c r="L16" t="n">
-        <v>0.12</v>
+        <v>1.7594</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3448</v>
+        <v>-2.6011</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2207</v>
+        <v>-0.9407</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5655</v>
+        <v>-1.6604</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.0006</v>
+        <v>1.1684</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.0011</v>
+        <v>-1.9474</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0006</v>
+        <v>3.1158</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4017</v>
+        <v>-0.5503</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3587</v>
+        <v>-0.4116</v>
       </c>
       <c r="U16" t="n">
-        <v>1.043</v>
+        <v>-0.1387</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7997</v>
+        <v>3.6116</v>
       </c>
       <c r="W16" t="n">
-        <v>2.6593</v>
+        <v>4.8326</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8597</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. RICARDO</t>
+          <t>A. GALLEGO CONTRERAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1697</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9211</v>
+        <v>-0.8917</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7514</v>
+        <v>0.9714</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.5164</v>
+        <v>-0.0618</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.6051</v>
+        <v>0.2755</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0887</v>
+        <v>-0.3373</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1213</v>
+        <v>-0.5013</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.7687</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6474</v>
+        <v>-0.5835</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3951</v>
+        <v>0.4396</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8365</v>
+        <v>0.1934</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5586</v>
+        <v>0.2461</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2003</v>
+        <v>0.3895</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0006</v>
+        <v>-0.1947</v>
       </c>
       <c r="R17" t="n">
-        <v>3.2009</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.0333</v>
+        <v>-0.248</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.6759</v>
+        <v>-0.1957</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3574</v>
+        <v>-0.0524</v>
       </c>
       <c r="V17" t="n">
-        <v>3.519</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>4.7188</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1538</v>
+        <v>-0.0452</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0445</v>
+        <v>0.0584</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1093</v>
+        <v>-0.1036</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3087</v>
+        <v>-0.3242</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1799</v>
+        <v>-0.1847</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1287</v>
+        <v>-0.1395</v>
       </c>
       <c r="J18" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3287</v>
+        <v>-0.3447</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1999</v>
+        <v>-0.2053</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1287</v>
+        <v>-0.1395</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0451</v>
+        <v>0.0842</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0645</v>
+        <v>0.0378</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0193</v>
+        <v>0.0464</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3329</v>
+        <v>-0.2345</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8772</v>
+        <v>-0.3151</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5443</v>
+        <v>0.0805</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7755</v>
+        <v>-0.7861</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1735</v>
+        <v>-1.1669</v>
       </c>
       <c r="I19" t="n">
-        <v>0.398</v>
+        <v>0.3808</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6909</v>
+        <v>1.8756</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0054</v>
+        <v>0.1002</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6855</v>
+        <v>1.7754</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4663</v>
+        <v>-2.6617</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1789</v>
+        <v>-1.2671</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2874</v>
+        <v>-1.3946</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R19" t="n">
-        <v>3.2009</v>
+        <v>3.1158</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3168</v>
+        <v>-0.2674</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1265</v>
+        <v>0.1062</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1903</v>
+        <v>-0.3736</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2409</v>
+        <v>-0.1547</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.2409</v>
+        <v>-0.1547</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. RAMIREZ PRIETO</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4246</v>
+        <v>-0.2759</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3957</v>
+        <v>-1.5658</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8203</v>
+        <v>1.2899</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4537</v>
+        <v>-3.304</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1356</v>
+        <v>-1.3408</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3181</v>
+        <v>-1.9631</v>
       </c>
       <c r="J20" t="n">
-        <v>0.04</v>
+        <v>-3.3739</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-1.583</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04</v>
+        <v>-1.7909</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4137</v>
+        <v>0.0699</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1356</v>
+        <v>0.2422</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2781</v>
+        <v>-0.1723</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2001</v>
+        <v>0.9737</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2001</v>
+        <v>1.1684</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3813</v>
+        <v>-0.1082</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3557</v>
+        <v>-0.4393</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0255</v>
+        <v>0.3311</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4596</v>
+        <v>2.1626</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.4421</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4596</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GALLEGO CONTRERAS</t>
+          <t>N. RAMIREZ PRIETO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5745</v>
+        <v>-0.656</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2337</v>
+        <v>0.0968</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6593</v>
+        <v>-0.7528</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0194</v>
+        <v>0.4327</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2868</v>
+        <v>0.1329</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3062</v>
+        <v>0.2998</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.518</v>
+        <v>0.0405</v>
       </c>
       <c r="K21" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.598</v>
+        <v>0.0405</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4986</v>
+        <v>0.3921</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2069</v>
+        <v>0.1329</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2918</v>
+        <v>0.2592</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2001</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6002</v>
+        <v>0.1947</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9552</v>
+        <v>0.2171</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5157</v>
+        <v>0.0563</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4395</v>
+        <v>0.1608</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.5005</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4222</v>
+        <v>-1.1892</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5578</v>
+        <v>-1.7087</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1356</v>
+        <v>0.5195</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2776</v>
+        <v>-2.758</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3491</v>
+        <v>-1.2257</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9285</v>
+        <v>-1.5323</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.4681</v>
+        <v>-1.2739</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.6341</v>
+        <v>-1.3955</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.834</v>
+        <v>0.1216</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1906</v>
+        <v>-1.4841</v>
       </c>
       <c r="N22" t="n">
-        <v>0.285</v>
+        <v>0.1698</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0945</v>
+        <v>-1.6539</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0003</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2001</v>
+        <v>-3.8947</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2003</v>
+        <v>1.9474</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2846</v>
+        <v>1.6846</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2891</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0045</v>
+        <v>0.9462</v>
       </c>
       <c r="V22" t="n">
-        <v>2.1398</v>
+        <v>1.8316</v>
       </c>
       <c r="W22" t="n">
-        <v>2.3995</v>
+        <v>2.7216</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2598</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. GARRIDO SOTO</t>
+          <t>J. RIBEIROS CARREIRAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2846</v>
+        <v>-1.4142</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6009</v>
+        <v>-0.5622</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6837</v>
+        <v>-0.852</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.0992</v>
+        <v>0.6717</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3822</v>
+        <v>2.5585</v>
       </c>
       <c r="I23" t="n">
-        <v>0.283</v>
+        <v>-1.8869</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2763</v>
+        <v>3.2859</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3963</v>
+        <v>3.3663</v>
       </c>
       <c r="L23" t="n">
-        <v>0.12</v>
+        <v>-0.0804</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8229</v>
+        <v>-2.6142</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9859</v>
+        <v>-0.8078</v>
       </c>
       <c r="O23" t="n">
-        <v>0.163</v>
+        <v>-1.8064</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4001</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2006</v>
+        <v>-4.0895</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8005</v>
+        <v>3.5053</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4144</v>
+        <v>-0.8911</v>
       </c>
       <c r="T23" t="n">
-        <v>1.6162</v>
+        <v>-0.3691</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2018</v>
+        <v>-0.5219</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.1998</v>
+        <v>-0.6105</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2598</v>
+        <v>0.6105</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4596</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. RIBEIROS CARREIRAS</t>
+          <t>F. GARRIDO SOTO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7063</v>
+        <v>-3.5628</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6395</v>
+        <v>-1.8734</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0669</v>
+        <v>-1.6894</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7072000000000001</v>
+        <v>-1.1655</v>
       </c>
       <c r="H24" t="n">
-        <v>2.5782</v>
+        <v>-1.3937</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.871</v>
+        <v>0.2282</v>
       </c>
       <c r="J24" t="n">
-        <v>3.0886</v>
+        <v>-0.2222</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2791</v>
+        <v>-0.3437</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1905</v>
+        <v>0.1216</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.3814</v>
+        <v>-0.9433</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7009</v>
+        <v>-1.05</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6805</v>
+        <v>0.1067</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6002</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.2012</v>
+        <v>-2.1421</v>
       </c>
       <c r="R24" t="n">
-        <v>3.601</v>
+        <v>1.7526</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.2135</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1268</v>
+        <v>0.2114</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0867</v>
+        <v>-0.9982</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5999</v>
+        <v>-1.2211</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5999</v>
+        <v>0.2795</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.1998</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.7706</v>
+        <v>-6.577</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.1288</v>
+        <v>-4.922</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6418</v>
+        <v>-1.655</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.3323</v>
+        <v>-4.4208</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3504</v>
+        <v>-0.4039</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.9819</v>
+        <v>-4.0169</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.1303</v>
+        <v>-2.0315</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4217</v>
+        <v>0.4644</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.552</v>
+        <v>-2.4959</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.202</v>
+        <v>-2.3893</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7721</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.4299</v>
+        <v>-1.521</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R25" t="n">
-        <v>3.0009</v>
+        <v>2.921</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.3246</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0024</v>
+        <v>0.0305</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.641</v>
+        <v>-0.3551</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-14.1289</v>
+        <v>-12.1137</v>
       </c>
       <c r="E26" t="n">
-        <v>-11.2338</v>
+        <v>-9.077200000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.8951</v>
+        <v>-3.0366</v>
       </c>
       <c r="G26" t="n">
-        <v>-13.9981</v>
+        <v>-14.1843</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.423999999999999</v>
+        <v>-5.316</v>
       </c>
       <c r="I26" t="n">
-        <v>-8.574</v>
+        <v>-8.868299999999998</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.159600000000001</v>
+        <v>-2.0475</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.598</v>
+        <v>-0.9152</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.5616</v>
+        <v>-1.1322</v>
       </c>
       <c r="M26" t="n">
-        <v>-10.8383</v>
+        <v>-12.1368</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.826</v>
+        <v>-4.401</v>
       </c>
       <c r="O26" t="n">
-        <v>-7.012200000000001</v>
+        <v>-7.7361</v>
       </c>
       <c r="P26" t="n">
-        <v>1.0003</v>
+        <v>0.9736000000000002</v>
       </c>
       <c r="Q26" t="n">
-        <v>-18.0052</v>
+        <v>-17.5262</v>
       </c>
       <c r="R26" t="n">
-        <v>19.0055</v>
+        <v>18.4999</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.2897</v>
+        <v>-1.1905</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4655</v>
+        <v>-0.2351000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.8244</v>
+        <v>-0.9554</v>
       </c>
       <c r="V26" t="n">
-        <v>2.1586</v>
+        <v>2.2874</v>
       </c>
       <c r="W26" t="n">
-        <v>10.3964</v>
+        <v>10.7316</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.238</v>
+        <v>-8.444299999999998</v>
       </c>
     </row>
   </sheetData>
